--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -1976,19 +1976,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>8982000</v>
+        <v>7635000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>20554</v>
+        <v>17471</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -17310,27 +17310,23 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H355" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I355" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H355" s="5" t="n">
+        <v>11966000</v>
+      </c>
+      <c r="I355" s="5" t="n">
+        <v>20883</v>
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18830,27 +18826,23 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H387" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I387" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H387" s="5" t="n">
+        <v>11591000</v>
+      </c>
+      <c r="I387" s="5" t="n">
+        <v>20229</v>
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -20350,27 +20342,23 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H419" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I419" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H419" s="5" t="n">
+        <v>11261000</v>
+      </c>
+      <c r="I419" s="5" t="n">
+        <v>19653</v>
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28748,7 +28736,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>27 套</t>
+          <t>26 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -28758,7 +28746,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>181 套</t>
+          <t>182 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -29070,12 +29058,12 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$898万
-$20,554/呎
-(在售)</t>
+$764万
+$17,471/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -31451,7 +31439,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>63 套</t>
+          <t>60 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -31461,7 +31449,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>158 套</t>
+          <t>161 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -32152,7 +32140,78 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1,197万
+$20,883/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>35/F</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$959万
+$17,536/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$942万
+$17,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1,110万
+$20,672/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1,067万
+$19,265/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32161,13 +32220,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>33/F</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32175,7 +32234,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32183,47 +32242,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$959万
-$17,536/呎
+$955万
+$17,466/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$942万
-$17,500/呎
+$938万
+$17,431/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1,110万
-$20,672/呎
+$1,106万
+$20,590/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$880万
-$17,193/呎
+$877万
+$17,125/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1,067万
-$19,265/呎
+$1,059万
+$19,112/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32232,13 +32291,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>32/F</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32246,7 +32305,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32254,47 +32313,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
+$952万
+$17,397/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$938万
-$17,431/呎
+$934万
+$17,362/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1,106万
-$20,590/呎
+$1,101万
+$20,508/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
+$1,048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1,059万
-$19,112/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
+$1,050万
+$18,958/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32303,13 +32362,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>31/F</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32317,7 +32376,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32325,47 +32384,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
+$937万
+$17,122/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$934万
-$17,362/呎
+$930万
+$17,294/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1,101万
-$20,508/呎
+$1,097万
+$20,426/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1,048万
-$20,469/呎
+$1,044万
+$20,387/呎
 (在售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1,050万
-$18,958/呎
+$1,042万
+$18,809/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1,159万
+$20,229/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>30/F</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+暂无价格
+暂无呎价
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1,093万
+$20,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1,040万
+$20,305/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1,034万
+$18,661/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32374,13 +32504,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>29/F</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32388,7 +32518,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32396,47 +32526,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$937万
-$17,122/呎
+$940万
+$17,190/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$930万
-$17,294/呎
+$923万
+$17,154/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1,097万
-$20,426/呎
+$1,088万
+$20,264/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1,044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
+$880万
+$17,191/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1,042万
-$18,809/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I18" s="18" t="inlineStr">
+$1,026万
+$18,511/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32445,13 +32575,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>28/F</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32459,7 +32589,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32467,47 +32597,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$944万
-$17,258/呎
+$938万
+$17,155/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
+$921万
+$17,121/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1,093万
-$20,346/呎
+$1,086万
+$20,223/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1,040万
-$20,305/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
+$878万
+$17,156/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1,034万
-$18,661/呎
+$1,022万
+$18,451/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -32516,13 +32646,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>27/F</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 暂无价格
@@ -32530,7 +32660,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 暂无价格
@@ -32538,148 +32668,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,088万
-$20,264/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,026万
-$18,511/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,086万
-$20,223/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,022万
-$18,451/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -32720,12 +32708,12 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1,126万
+$19,653/呎
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4675,7 +4541,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6187,7 +6053,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -9433,7 +9299,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -21625,7 +21491,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -26035,7 +25901,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -26411,7 +26277,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -26787,7 +26653,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -27163,7 +27029,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -27539,7 +27405,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -28053,7 +27919,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -28667,5552 +28533,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海德园第1期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>288 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>182 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>60 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 938呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 923呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$940万
-$18,000/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,117万
-$21,556/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$777万
-$17,785/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$742万
-$17,751/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 571呎 (2房)
-$1,236万
-$21,651/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$933万
-$17,874/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$943万
-$18,197/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$772万
-$17,664/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$737万
-$17,627/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,215万
-$21,208/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$926万
-$17,749/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,101万
-$21,257/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$766万
-$17,538/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$732万
-$17,505/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,160万
-$21,556/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,190万
-$20,771/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$923万
-$17,678/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$932万
-$17,998/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$764万
-$17,471/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$729万
-$17,435/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,172万
-$20,445/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,095万
-$21,131/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$762万
-$17,435/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$753万
-$18,014/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,143万
-$21,238/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,159万
-$20,222/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$916万
-$17,538/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,088万
-$21,004/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$757万
-$17,332/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$723万
-$17,297/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,129万
-$20,987/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,145万
-$19,983/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$901万
-$17,264/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$921万
-$17,782/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$754万
-$17,263/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$720万
-$17,227/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,120万
-$20,818/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,136万
-$19,824/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$908万
-$17,398/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,079万
-$20,838/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$751万
-$17,192/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$717万
-$17,158/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,127万
-$19,665/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$905万
-$17,330/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$914万
-$17,641/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$748万
-$17,124/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$714万
-$17,089/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,118万
-$19,510/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$901万
-$17,261/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$910万
-$17,571/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$745万
-$17,057/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$712万
-$17,022/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,109万
-$19,354/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$897万
-$17,192/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$906万
-$17,500/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$742万
-$16,989/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$709万
-$16,955/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,100万
-$19,201/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$903万
-$17,432/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$739万
-$16,920/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$706万
-$16,885/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,076万
-$20,007/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,092万
-$19,049/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$890万
-$17,056/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$899万
-$17,363/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$736万
-$16,854/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$703万
-$16,818/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,083万
-$18,897/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$888万
-$17,021/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1,056万
-$20,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$735万
-$16,819/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$702万
-$16,787/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,064万
-$19,783/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,079万
-$18,836/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$883万
-$16,920/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$892万
-$17,224/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$731万
-$16,721/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$698万
-$16,687/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,069万
-$18,654/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$880万
-$16,852/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$889万
-$17,156/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$728万
-$16,652/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$719万
-$17,206/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,064万
-$18,562/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,377万
-$26,445/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$876万
-$16,785/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$885万
-$17,087/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$725万
-$16,586/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$692万
-$16,553/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,027万
-$17,925/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,348万
-$26,118/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$873万
-$16,718/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$882万
-$17,019/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$722万
-$16,519/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$689万
-$16,488/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,053万
-$18,379/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,318万
-$25,783/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$869万
-$16,651/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$878万
-$16,952/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$719万
-$16,455/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$711万
-$17,002/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,048万
-$18,286/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,288万
-$25,452/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$856万
-$16,389/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$875万
-$16,884/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$716万
-$16,389/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$684万
-$16,356/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,043万
-$18,195/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,259万
-$25,125/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$883万
-$16,908/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$871万
-$16,817/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$713万
-$16,323/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$681万
-$16,289/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,074万
-$18,743/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,230万
-$24,803/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$859万
-$16,452/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$868万
-$16,749/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$710万
-$16,259/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$702万
-$16,799/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,069万
-$18,651/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,215万
-$24,643/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$857万
-$16,420/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$866万
-$16,716/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$709万
-$16,227/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$677万
-$16,194/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,015万
-$18,872/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,030万
-$17,970/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,173万
-$24,171/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$852万
-$16,322/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$861万
-$16,616/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$705万
-$16,128/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$673万
-$16,098/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,008万
-$18,732/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,022万
-$17,836/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,145万
-$23,861/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$849万
-$16,257/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$857万
-$16,550/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$702万
-$16,064/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$670万
-$16,033/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1,003万
-$18,638/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,017万
-$17,747/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,126万
-$23,648/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$845万
-$16,192/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$854万
-$16,485/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$699万
-$16,000/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$668万
-$15,969/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,012万
-$17,658/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,107万
-$23,437/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$842万
-$16,128/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$850万
-$16,419/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$696万
-$15,938/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$665万
-$15,907/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,007万
-$17,571/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,096万
-$23,320/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$838万
-$16,063/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$847万
-$16,353/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$694万
-$15,874/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$686万
-$16,402/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$988万
-$18,362/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,002万
-$17,483/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,086万
-$23,205/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$835万
-$15,992/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$843万
-$16,280/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$690万
-$15,801/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$659万
-$15,773/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H34" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$997万
-$17,396/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,076万
-$23,089/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$831万
-$15,920/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$840万
-$16,207/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$688万
-$15,732/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$656万
-$15,701/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$978万
-$18,180/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$992万
-$17,311/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,065万
-$22,974/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$827万
-$15,841/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$835万
-$16,125/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$684万
-$15,654/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$653万
-$15,624/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$973万
-$18,089/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$987万
-$17,223/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,060万
-$22,917/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$815万
-$15,615/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$833万
-$16,087/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$682万
-$15,616/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$674万
-$16,132/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$971万
-$18,045/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$973万
-$16,979/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,045万
-$22,746/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$819万
-$15,684/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$827万
-$15,967/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$677万
-$15,499/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$639万
-$15,285/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$966万
-$16,853/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,035万
-$22,633/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$805万
-$15,423/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$823万
-$15,888/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$674万
-$15,421/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$643万
-$15,392/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$972万
-$16,967/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2,024万
-$22,515/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$811万
-$15,529/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$819万
-$15,807/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$671万
-$15,346/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$633万
-$15,148/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$968万
-$16,885/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 866呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 854呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>C | 501呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="16" t="inlineStr">
-        <is>
-          <t>D | 496呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F41" s="16" t="inlineStr">
-        <is>
-          <t>E | 416呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>F | 397呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t>G | 501呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>H | 535呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海德园第1期 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>304 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>60 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>161 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>83 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>45/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 938呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 923呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$1,039万
-$18,987/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$1,178万
-$21,900/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,158万
-$21,557/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,102万
-$21,514/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,175万
-$21,215/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>H | 571呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>43/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$1,023万
-$18,707/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$1,170万
-$21,747/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,150万
-$21,408/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,094万
-$21,365/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,158万
-$20,903/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>42/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$1,008万
-$18,431/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$1,162万
-$21,597/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,142万
-$21,259/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,086万
-$21,217/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,141万
-$20,592/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I8" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>41/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$996万
-$18,212/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$1,157万
-$21,511/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,137万
-$21,173/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,082万
-$21,133/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,127万
-$20,348/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$984万
-$17,996/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$1,153万
-$21,426/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,132万
-$21,089/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,078万
-$21,047/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,114万
-$20,106/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I10" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$977万
-$17,854/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$976万
-$18,139/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,128万
-$21,006/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,073万
-$20,963/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,103万
-$19,908/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$973万
-$17,782/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$955万
-$17,747/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,126万
-$20,965/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$893万
-$17,436/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,097万
-$19,809/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$967万
-$17,676/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$949万
-$17,641/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,119万
-$20,838/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$887万
-$17,330/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,084万
-$19,574/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$963万
-$17,607/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$945万
-$17,572/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,115万
-$20,756/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$884万
-$17,262/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,076万
-$19,419/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,197万
-$20,883/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$959万
-$17,536/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$942万
-$17,500/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,110万
-$20,672/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,193/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,067万
-$19,265/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$938万
-$17,431/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,106万
-$20,590/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,059万
-$19,112/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,101万
-$20,508/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,048万
-$20,469/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,050万
-$18,958/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,097万
-$20,426/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,042万
-$18,809/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,159万
-$20,229/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,093万
-$20,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1,040万
-$20,305/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,034万
-$18,661/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,088万
-$20,264/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,026万
-$18,511/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,086万
-$20,223/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,022万
-$18,451/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,080万
-$20,102/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,012万
-$18,274/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,126万
-$19,653/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,075万
-$20,022/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$996万
-$17,969/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,071万
-$19,944/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1,002万
-$18,092/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$922万
-$16,850/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,062万
-$19,784/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$914万
-$16,715/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$887万
-$16,487/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1,058万
-$19,706/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$839万
-$16,389/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$987万
-$17,823/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$911万
-$16,649/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,615/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$878万
-$16,356/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$836万
-$16,324/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$982万
-$17,735/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$907万
-$16,581/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$922万
-$17,134/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$875万
-$16,291/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$832万
-$16,258/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$978万
-$17,648/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$905万
-$16,550/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$889万
-$16,517/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$873万
-$16,259/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$831万
-$16,227/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$964万
-$17,395/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$900万
-$16,452/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$883万
-$16,418/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$868万
-$16,162/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$826万
-$16,131/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$968万
-$17,471/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$896万
-$16,384/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$870万
-$16,162/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$864万
-$16,099/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$822万
-$16,064/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$963万
-$17,384/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$893万
-$16,320/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$876万
-$16,288/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$861万
-$16,034/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$819万
-$16,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$992万
-$17,908/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>13/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$889万
-$16,256/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$873万
-$16,223/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$858万
-$15,970/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$816万
-$15,938/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H34" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$954万
-$17,211/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$886万
-$16,190/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$869万
-$16,158/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$854万
-$15,907/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$813万
-$15,875/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$949万
-$17,128/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,045万
-$18,237/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$882万
-$16,117/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$866万
-$16,087/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$850万
-$15,834/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$809万
-$15,803/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$944万
-$17,042/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,040万
-$18,147/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$878万
-$16,046/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$862万
-$16,015/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$846万
-$15,764/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$834万
-$16,287/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H37" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$939万
-$16,957/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,035万
-$18,056/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$873万
-$15,965/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E38" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$888万
-$16,498/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$859万
-$15,998/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$802万
-$15,654/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$924万
-$16,673/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,029万
-$17,965/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$872万
-$15,934/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$886万
-$16,463/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$857万
-$15,966/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$790万
-$15,438/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$932万
-$16,830/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,027万
-$17,921/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$866万
-$15,839/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$850万
-$15,807/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$852万
-$15,872/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$795万
-$15,529/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H40" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$926万
-$16,706/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,019万
-$17,787/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="65" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$862万
-$15,761/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E41" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$846万
-$15,730/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$848万
-$15,791/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$791万
-$15,453/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$921万
-$16,623/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,014万
-$17,698/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="65" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$858万
-$15,682/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$842万
-$15,651/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$844万
-$15,715/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$788万
-$15,398/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="H42" s="17" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$916万
-$16,540/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1,009万
-$17,611/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>A | 866呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>B | 854呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>C | 526呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>D | 517呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
-        <is>
-          <t>E | 515呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>G | 517呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>H | 535呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -28533,4 +28721,5552 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 938呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 923呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$940万
+$18,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1117万
+$21,556/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$777万
+$17,785/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$742万
+$17,751/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 571呎 (2房)
+$1236万
+$21,651/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$933万
+$17,874/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$943万
+$18,197/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$772万
+$17,664/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$737万
+$17,627/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1215万
+$21,208/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$926万
+$17,749/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1101万
+$21,257/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$766万
+$17,538/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$732万
+$17,505/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1160万
+$21,556/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1190万
+$20,771/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$923万
+$17,678/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$932万
+$17,998/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$764万
+$17,471/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$729万
+$17,435/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1172万
+$20,445/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$894万
+$17,125/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1095万
+$21,131/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$762万
+$17,435/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$753万
+$18,014/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1143万
+$21,238/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,222/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$916万
+$17,538/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1088万
+$21,004/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$757万
+$17,332/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$723万
+$17,297/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1129万
+$20,987/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1145万
+$19,983/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$901万
+$17,264/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$921万
+$17,782/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$754万
+$17,263/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$720万
+$17,227/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1120万
+$20,818/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1136万
+$19,824/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$908万
+$17,398/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1079万
+$20,838/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$751万
+$17,192/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$717万
+$17,158/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1127万
+$19,665/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$905万
+$17,330/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$914万
+$17,641/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$748万
+$17,124/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$714万
+$17,089/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1118万
+$19,510/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$901万
+$17,261/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$910万
+$17,571/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$745万
+$17,057/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$712万
+$17,022/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1109万
+$19,354/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$897万
+$17,192/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$906万
+$17,500/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$742万
+$16,989/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$709万
+$16,955/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1100万
+$19,201/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$894万
+$17,125/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$903万
+$17,432/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$739万
+$16,920/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$706万
+$16,885/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1076万
+$20,007/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1092万
+$19,049/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$890万
+$17,056/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$899万
+$17,363/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$736万
+$16,854/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$703万
+$16,818/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1083万
+$18,897/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$888万
+$17,021/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1056万
+$20,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$735万
+$16,819/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$702万
+$16,787/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1064万
+$19,783/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1079万
+$18,836/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$883万
+$16,920/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$892万
+$17,224/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$731万
+$16,721/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$698万
+$16,687/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1069万
+$18,654/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$880万
+$16,852/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$889万
+$17,156/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$728万
+$16,652/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$719万
+$17,206/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1064万
+$18,562/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2377万
+$26,445/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$876万
+$16,785/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$885万
+$17,087/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$725万
+$16,586/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$692万
+$16,553/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1027万
+$17,925/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2348万
+$26,118/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$873万
+$16,718/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$882万
+$17,019/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$722万
+$16,519/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$689万
+$16,488/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1053万
+$18,379/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2318万
+$25,783/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$869万
+$16,651/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$878万
+$16,952/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$719万
+$16,455/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$711万
+$17,002/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1048万
+$18,286/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2288万
+$25,452/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$856万
+$16,389/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$875万
+$16,884/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$716万
+$16,389/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$684万
+$16,356/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1043万
+$18,195/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2259万
+$25,125/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$883万
+$16,908/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$871万
+$16,817/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$713万
+$16,323/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$681万
+$16,289/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1074万
+$18,743/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2230万
+$24,803/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$859万
+$16,452/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$868万
+$16,749/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$710万
+$16,259/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$702万
+$16,799/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1069万
+$18,651/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2215万
+$24,643/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$857万
+$16,420/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$866万
+$16,716/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$709万
+$16,227/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$677万
+$16,194/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1015万
+$18,872/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1030万
+$17,970/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2173万
+$24,171/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$852万
+$16,322/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$861万
+$16,616/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$705万
+$16,128/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$673万
+$16,098/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1008万
+$18,732/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1022万
+$17,836/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2145万
+$23,861/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$849万
+$16,257/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$857万
+$16,550/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$702万
+$16,064/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$670万
+$16,033/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1003万
+$18,638/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1017万
+$17,747/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2126万
+$23,648/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$845万
+$16,192/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$854万
+$16,485/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$699万
+$16,000/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$668万
+$15,969/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1012万
+$17,658/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2107万
+$23,437/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$842万
+$16,128/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$850万
+$16,419/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$696万
+$15,938/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$665万
+$15,907/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1007万
+$17,571/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2096万
+$23,320/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$838万
+$16,063/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$847万
+$16,353/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$694万
+$15,874/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$686万
+$16,402/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$988万
+$18,362/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1002万
+$17,483/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2086万
+$23,205/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$835万
+$15,992/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$843万
+$16,280/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$690万
+$15,801/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$659万
+$15,773/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$997万
+$17,396/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2076万
+$23,089/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$831万
+$15,920/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$840万
+$16,207/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$688万
+$15,732/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$656万
+$15,701/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$978万
+$18,180/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$992万
+$17,311/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2065万
+$22,974/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$827万
+$15,841/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$835万
+$16,125/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$684万
+$15,654/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$653万
+$15,624/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$973万
+$18,089/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$987万
+$17,223/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2060万
+$22,917/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$815万
+$15,615/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$833万
+$16,087/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$682万
+$15,616/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$674万
+$16,132/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$971万
+$18,045/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$973万
+$16,979/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2045万
+$22,746/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$819万
+$15,684/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$827万
+$15,967/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$677万
+$15,499/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$639万
+$15,285/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$966万
+$16,853/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2035万
+$22,633/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$805万
+$15,423/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$823万
+$15,888/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$674万
+$15,421/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$643万
+$15,392/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$972万
+$16,967/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2024万
+$22,515/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$811万
+$15,529/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$819万
+$15,807/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$671万
+$15,346/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$633万
+$15,148/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$968万
+$16,885/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 866呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 854呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>C | 501呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>D | 496呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>E | 416呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>F | 397呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>G | 501呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I40" s="20" t="inlineStr">
+        <is>
+          <t>H | 535呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 938呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 923呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$1039万
+$18,987/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$1178万
+$21,900/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1158万
+$21,557/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1102万
+$21,514/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1175万
+$21,215/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>H | 571呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$1023万
+$18,707/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$1170万
+$21,747/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1150万
+$21,408/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1094万
+$21,365/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1158万
+$20,903/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$1008万
+$18,431/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$1162万
+$21,597/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1142万
+$21,259/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1086万
+$21,217/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1141万
+$20,592/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$996万
+$18,212/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$1157万
+$21,511/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1137万
+$21,173/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1082万
+$21,133/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1127万
+$20,348/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$984万
+$17,996/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$1153万
+$21,426/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1132万
+$21,089/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1078万
+$21,047/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1114万
+$20,106/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$977万
+$17,854/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$976万
+$18,139/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1128万
+$21,006/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1073万
+$20,963/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1103万
+$19,908/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$973万
+$17,782/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$955万
+$17,747/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1126万
+$20,965/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$893万
+$17,436/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1097万
+$19,809/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$967万
+$17,676/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$949万
+$17,641/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1119万
+$20,838/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$887万
+$17,330/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1084万
+$19,574/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$963万
+$17,607/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$945万
+$17,572/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1115万
+$20,756/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$884万
+$17,262/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1076万
+$19,419/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1197万
+$20,883/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$959万
+$17,536/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$942万
+$17,500/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1110万
+$20,672/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1067万
+$19,265/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$955万
+$17,466/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$938万
+$17,431/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1106万
+$20,590/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$877万
+$17,125/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1059万
+$19,112/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$952万
+$17,397/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$934万
+$17,362/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1101万
+$20,508/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1050万
+$18,958/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$937万
+$17,122/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$930万
+$17,294/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1097万
+$20,426/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1044万
+$20,387/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1042万
+$18,809/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,229/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1093万
+$20,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1040万
+$20,305/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1034万
+$18,661/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$940万
+$17,190/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$923万
+$17,154/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1088万
+$20,264/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,191/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1026万
+$18,511/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$938万
+$17,155/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$921万
+$17,121/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1086万
+$20,223/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$933万
+$17,053/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$905万
+$16,818/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1080万
+$20,102/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$856万
+$16,719/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1012万
+$18,274/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1126万
+$19,653/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$902万
+$16,484/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$912万
+$16,952/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1075万
+$20,022/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$853万
+$16,652/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$996万
+$17,969/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$914万
+$16,718/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$908万
+$16,885/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1071万
+$19,944/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$849万
+$16,586/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1002万
+$18,092/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$922万
+$16,850/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$894万
+$16,619/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$907万
+$16,885/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$846万
+$16,520/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$986万
+$17,791/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$918万
+$16,782/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$901万
+$16,751/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1062万
+$19,784/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$842万
+$16,453/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$992万
+$17,913/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$914万
+$16,715/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$887万
+$16,487/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1058万
+$19,706/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$839万
+$16,389/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$987万
+$17,823/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$911万
+$16,649/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$894万
+$16,615/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$878万
+$16,356/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$836万
+$16,324/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$982万
+$17,735/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$907万
+$16,581/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$922万
+$17,134/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$875万
+$16,291/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$832万
+$16,258/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$978万
+$17,648/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$905万
+$16,550/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$889万
+$16,517/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$873万
+$16,259/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$831万
+$16,227/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$964万
+$17,395/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$900万
+$16,452/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$883万
+$16,418/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$868万
+$16,162/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$826万
+$16,131/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$968万
+$17,471/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$896万
+$16,384/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$870万
+$16,162/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$864万
+$16,099/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$822万
+$16,064/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$963万
+$17,384/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$893万
+$16,320/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$876万
+$16,288/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$861万
+$16,034/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$819万
+$16,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$992万
+$17,908/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$889万
+$16,256/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$873万
+$16,223/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$858万
+$15,970/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$816万
+$15,938/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$954万
+$17,211/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$886万
+$16,190/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$869万
+$16,158/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$854万
+$15,907/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$813万
+$15,875/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$949万
+$17,128/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1045万
+$18,237/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$882万
+$16,117/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$866万
+$16,087/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$850万
+$15,834/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$809万
+$15,803/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$944万
+$17,042/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1040万
+$18,147/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$878万
+$16,046/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$862万
+$16,015/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$846万
+$15,764/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$834万
+$16,287/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$939万
+$16,957/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1035万
+$18,056/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$873万
+$15,965/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$888万
+$16,498/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$859万
+$15,998/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$802万
+$15,654/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$924万
+$16,673/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1029万
+$17,965/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$872万
+$15,934/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$886万
+$16,463/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$857万
+$15,966/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$790万
+$15,438/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$932万
+$16,830/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1027万
+$17,921/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$866万
+$15,839/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$850万
+$15,807/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$852万
+$15,872/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$795万
+$15,529/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H39" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$926万
+$16,706/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I39" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1019万
+$17,787/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$862万
+$15,761/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$846万
+$15,730/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$848万
+$15,791/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$791万
+$15,453/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H40" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$921万
+$16,623/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1014万
+$17,698/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$858万
+$15,682/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$842万
+$15,651/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$844万
+$15,715/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$788万
+$15,398/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H41" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$916万
+$16,540/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="I41" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1009万
+$17,611/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>A | 866呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>B | 854呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>C | 526呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>D | 517呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>E | 515呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>G | 517呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I42" s="20" t="inlineStr">
+        <is>
+          <t>H | 535呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -26603,7 +26603,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -28967,7 +28967,7 @@
           <t>D | 518呎 (2房)
 $943万
 $18,197/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -29046,7 +29046,7 @@
           <t>E | 437呎 (1房)
 $766万
 $17,538/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>D | 518呎 (2房)
 $932万
 $17,998/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -29259,7 +29259,7 @@
           <t>E | 437呎 (1房)
 $757万
 $17,332/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -29330,7 +29330,7 @@
           <t>E | 437呎 (1房)
 $754万
 $17,263/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -29701,7 +29701,7 @@
           <t>G | 538呎 (2房)
 $1076万
 $20,007/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -30482,7 +30482,7 @@
           <t>G | 538呎 (2房)
 $1015万
 $18,872/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -31954,7 +31954,7 @@
           <t>D | 538呎 (2房)
 $976万
 $18,139/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -33879,7 +33879,7 @@
           <t>E | 537呎 (2房)
 $859万
 $15,998/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">

--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -9444,18 +9444,18 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>20207900</v>
+        <v>21634340</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>22478</v>
+        <v>24065</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N137" s="3" t="inlineStr">
@@ -9956,18 +9956,18 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>19958000</v>
+        <v>21366800</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>22200</v>
+        <v>23767</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -10468,18 +10468,18 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>19702150</v>
+        <v>21092890</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>21916</v>
+        <v>23463</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -10980,18 +10980,18 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>19448850</v>
+        <v>20821710</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>21634</v>
+        <v>23161</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N161" s="3" t="inlineStr">
@@ -11492,18 +11492,18 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>19198950</v>
+        <v>20554170</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>21356</v>
+        <v>22863</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -12004,18 +12004,18 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K177" s="5" t="n">
-        <v>18953300</v>
+        <v>20291180</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>21083</v>
+        <v>22571</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr">
@@ -12508,18 +12508,18 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
-        <v>18830900</v>
+        <v>20160140</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>20946</v>
+        <v>22425</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N185" s="3" t="inlineStr">
@@ -13012,18 +13012,18 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K193" s="5" t="n">
-        <v>18470500</v>
+        <v>19774300</v>
       </c>
       <c r="L193" s="5" t="n">
-        <v>20546</v>
+        <v>21996</v>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -13516,18 +13516,18 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K201" s="5" t="n">
-        <v>18233350</v>
+        <v>19520410</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>20282</v>
+        <v>21713</v>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -14028,18 +14028,18 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K209" s="5" t="n">
-        <v>18071000</v>
+        <v>19346600</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>20101</v>
+        <v>21520</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -14540,18 +14540,18 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K217" s="5" t="n">
-        <v>17909500</v>
+        <v>19173700</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>19922</v>
+        <v>21328</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
@@ -15044,18 +15044,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>17820250</v>
+        <v>19078150</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>19822</v>
+        <v>21222</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -15548,18 +15548,18 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>17731850</v>
+        <v>18983510</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>19724</v>
+        <v>21116</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -16052,18 +16052,18 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>17643450</v>
+        <v>18888870</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>19626</v>
+        <v>21011</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
@@ -16556,18 +16556,18 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>17555900</v>
+        <v>18795140</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>19528</v>
+        <v>20907</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
@@ -17060,18 +17060,18 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K257" s="5" t="n">
-        <v>17511700</v>
+        <v>18747820</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>19479</v>
+        <v>20854</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
@@ -17564,18 +17564,18 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>17381650</v>
+        <v>18608590</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>19334</v>
+        <v>20699</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
@@ -18068,18 +18068,18 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K273" s="5" t="n">
-        <v>17294950</v>
+        <v>18515770</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>19238</v>
+        <v>20596</v>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
@@ -18580,18 +18580,18 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>17204850</v>
+        <v>18419310</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>19138</v>
+        <v>20489</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>建築期付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">

--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4640,34 +4640,34 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>10794000</v>
+        <v>9175000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>20838</v>
+        <v>17712</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>9174900</v>
+        <v>9175000</v>
       </c>
       <c r="L63" s="5" t="n">
         <v>17712</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -18246,38 +18246,30 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>9540000</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>17732</v>
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K276" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L276" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K276" s="5" t="n">
+        <v>9540000</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>17732</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
@@ -18286,7 +18278,7 @@
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37567,7 +37559,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -39010,7 +39002,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39020,7 +39012,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39282,7 +39274,7 @@
           <t>G | 538呎 (2房)
 $1160万
 $21,556/呎
-(26年-06月-27日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -39542,7 +39534,7 @@
           <t>D | 518呎 (2房)
 $921万
 $17,782/呎
-(26年-06月-08日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -39566,7 +39558,7 @@
           <t>G | 538呎 (2房)
 $1120万
 $20,818/呎
-(26年-06月-19日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -39608,12 +39600,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1079万
-$20,838/呎
-(在售)</t>
+$918万
+$17,712/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -41549,12 +41541,12 @@
 (25年-09月-28日)</t>
         </is>
       </c>
-      <c r="H39" s="22" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
+$954万
+$17,732/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -44312,7 +44304,7 @@
           <t>E | 537呎 (2房)
 $848万
 $15,791/呎
-(26年-06月-08日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">

--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -39100,7 +39100,7 @@
           <t>C | 522呎 (2房)
 $940万
 $18,000/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39116,7 +39116,7 @@
           <t>E | 437呎 (1房)
 $777万
 $17,785/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -39124,7 +39124,7 @@
           <t>F | 418呎 (1房)
 $742万
 $17,751/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -39140,7 +39140,7 @@
           <t>H | 571呎 (2房)
 $1236万
 $21,651/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39171,7 +39171,7 @@
           <t>C | 522呎 (2房)
 $933万
 $17,874/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -39179,7 +39179,7 @@
           <t>D | 518呎 (2房)
 $943万
 $18,197/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -39187,7 +39187,7 @@
           <t>E | 437呎 (1房)
 $772万
 $17,664/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -39195,7 +39195,7 @@
           <t>F | 418呎 (1房)
 $737万
 $17,627/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -39211,7 +39211,7 @@
           <t>H | 573呎 (2房)
 $1215万
 $21,208/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39242,7 +39242,7 @@
           <t>C | 522呎 (2房)
 $926万
 $17,749/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39258,7 +39258,7 @@
           <t>E | 437呎 (1房)
 $766万
 $17,538/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -39266,7 +39266,7 @@
           <t>F | 418呎 (1房)
 $732万
 $17,505/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -39274,7 +39274,7 @@
           <t>G | 538呎 (2房)
 $1160万
 $21,556/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -39282,7 +39282,7 @@
           <t>H | 573呎 (2房)
 $1190万
 $20,771/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39313,7 +39313,7 @@
           <t>C | 522呎 (2房)
 $923万
 $17,678/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -39321,7 +39321,7 @@
           <t>D | 518呎 (2房)
 $932万
 $17,998/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -39329,7 +39329,7 @@
           <t>E | 437呎 (1房)
 $764万
 $17,471/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -39337,7 +39337,7 @@
           <t>F | 418呎 (1房)
 $729万
 $17,435/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -39353,7 +39353,7 @@
           <t>H | 573呎 (2房)
 $1172万
 $20,445/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39384,7 +39384,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -39392,7 +39392,7 @@
           <t>D | 518呎 (2房)
 $930万
 $17,961/呎
-(26年-07月-10日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -39400,7 +39400,7 @@
           <t>E | 437呎 (1房)
 $762万
 $17,435/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -39408,7 +39408,7 @@
           <t>F | 418呎 (1房)
 $753万
 $18,014/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -39416,7 +39416,7 @@
           <t>G | 538呎 (2房)
 $1143万
 $21,238/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -39424,7 +39424,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,222/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -39455,7 +39455,7 @@
           <t>C | 522呎 (2房)
 $916万
 $17,538/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -39463,7 +39463,7 @@
           <t>D | 518呎 (2房)
 $925万
 $17,853/呎
-(26年-07月-11日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -39471,7 +39471,7 @@
           <t>E | 437呎 (1房)
 $757万
 $17,332/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -39479,7 +39479,7 @@
           <t>F | 418呎 (1房)
 $723万
 $17,297/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -39487,7 +39487,7 @@
           <t>G | 538呎 (2房)
 $1129万
 $20,987/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -39495,7 +39495,7 @@
           <t>H | 573呎 (2房)
 $1145万
 $19,983/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39526,7 +39526,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,264/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -39534,7 +39534,7 @@
           <t>D | 518呎 (2房)
 $921万
 $17,782/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -39542,7 +39542,7 @@
           <t>E | 437呎 (1房)
 $754万
 $17,263/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>F | 418呎 (1房)
 $720万
 $17,227/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>G | 538呎 (2房)
 $1120万
 $20,818/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -39566,7 +39566,7 @@
           <t>H | 573呎 (2房)
 $1136万
 $19,824/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39597,7 @@
           <t>C | 522呎 (2房)
 $908万
 $17,398/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>D | 518呎 (2房)
 $918万
 $17,712/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>E | 437呎 (1房)
 $751万
 $17,192/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>F | 418呎 (1房)
 $717万
 $17,158/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>H | 573呎 (2房)
 $1127万
 $19,665/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39668,7 +39668,7 @@
           <t>C | 522呎 (2房)
 $905万
 $17,330/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 518呎 (2房)
 $914万
 $17,641/呎
-(26年-06月-26日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 437呎 (1房)
 $748万
 $17,124/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 418呎 (1房)
 $714万
 $17,089/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -39708,7 +39708,7 @@
           <t>H | 573呎 (2房)
 $1118万
 $19,510/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39739,7 +39739,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,261/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>D | 518呎 (2房)
 $910万
 $17,571/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -39755,7 +39755,7 @@
           <t>E | 437呎 (1房)
 $745万
 $17,057/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -39763,7 +39763,7 @@
           <t>F | 418呎 (1房)
 $712万
 $17,022/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -39779,7 +39779,7 @@
           <t>H | 573呎 (2房)
 $1109万
 $19,354/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
           <t>C | 522呎 (2房)
 $897万
 $17,192/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -39818,7 +39818,7 @@
           <t>D | 518呎 (2房)
 $906万
 $17,500/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -39826,7 +39826,7 @@
           <t>E | 437呎 (1房)
 $742万
 $16,989/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -39834,7 +39834,7 @@
           <t>F | 418呎 (1房)
 $709万
 $16,955/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -39850,7 +39850,7 @@
           <t>H | 573呎 (2房)
 $1100万
 $19,201/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39881,7 +39881,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -39889,7 +39889,7 @@
           <t>D | 518呎 (2房)
 $903万
 $17,432/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -39897,7 +39897,7 @@
           <t>E | 437呎 (1房)
 $739万
 $16,920/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -39905,7 +39905,7 @@
           <t>F | 418呎 (1房)
 $706万
 $16,885/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -39913,7 +39913,7 @@
           <t>G | 538呎 (2房)
 $1076万
 $20,007/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -39921,7 +39921,7 @@
           <t>H | 573呎 (2房)
 $1092万
 $19,049/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -39952,7 +39952,7 @@
           <t>C | 522呎 (2房)
 $890万
 $17,056/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -39960,7 +39960,7 @@
           <t>D | 518呎 (2房)
 $899万
 $17,363/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -39968,7 +39968,7 @@
           <t>E | 437呎 (1房)
 $736万
 $16,854/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -39976,7 +39976,7 @@
           <t>F | 418呎 (1房)
 $703万
 $16,818/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -39992,7 +39992,7 @@
           <t>H | 573呎 (2房)
 $1083万
 $18,897/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -40023,7 +40023,7 @@
           <t>C | 522呎 (2房)
 $888万
 $17,021/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -40039,7 +40039,7 @@
           <t>E | 437呎 (1房)
 $735万
 $16,819/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -40047,7 +40047,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,787/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -40055,7 +40055,7 @@
           <t>G | 538呎 (2房)
 $1064万
 $19,783/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -40063,7 +40063,7 @@
           <t>H | 573呎 (2房)
 $1079万
 $18,836/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -40094,7 +40094,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,920/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -40102,7 +40102,7 @@
           <t>D | 518呎 (2房)
 $892万
 $17,224/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -40110,7 +40110,7 @@
           <t>E | 437呎 (1房)
 $731万
 $16,721/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -40118,7 +40118,7 @@
           <t>F | 418呎 (1房)
 $698万
 $16,687/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -40134,7 +40134,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,654/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40165,7 +40165,7 @@
           <t>C | 522呎 (2房)
 $880万
 $16,852/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -40173,7 +40173,7 @@
           <t>D | 518呎 (2房)
 $889万
 $17,156/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -40181,7 +40181,7 @@
           <t>E | 437呎 (1房)
 $728万
 $16,652/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -40189,7 +40189,7 @@
           <t>F | 418呎 (1房)
 $719万
 $17,206/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -40205,7 +40205,7 @@
           <t>H | 573呎 (2房)
 $1064万
 $18,562/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
           <t>C | 522呎 (2房)
 $876万
 $16,785/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -40244,7 +40244,7 @@
           <t>D | 518呎 (2房)
 $885万
 $17,087/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40252,7 +40252,7 @@
           <t>E | 437呎 (1房)
 $725万
 $16,586/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -40260,7 +40260,7 @@
           <t>F | 418呎 (1房)
 $692万
 $16,553/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -40276,7 +40276,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,925/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -40307,7 +40307,7 @@
           <t>C | 522呎 (2房)
 $873万
 $16,718/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -40315,7 +40315,7 @@
           <t>D | 518呎 (2房)
 $882万
 $17,019/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40323,7 +40323,7 @@
           <t>E | 437呎 (1房)
 $722万
 $16,519/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -40331,7 +40331,7 @@
           <t>F | 418呎 (1房)
 $689万
 $16,488/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -40347,7 +40347,7 @@
           <t>H | 573呎 (2房)
 $1053万
 $18,379/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -40378,7 +40378,7 @@
           <t>C | 522呎 (2房)
 $869万
 $16,651/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -40386,7 +40386,7 @@
           <t>D | 518呎 (2房)
 $878万
 $16,952/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -40394,7 +40394,7 @@
           <t>E | 437呎 (1房)
 $719万
 $16,455/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -40402,7 +40402,7 @@
           <t>F | 418呎 (1房)
 $711万
 $17,002/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -40418,7 +40418,7 @@
           <t>H | 573呎 (2房)
 $1048万
 $18,286/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40449,7 +40449,7 @@
           <t>C | 522呎 (2房)
 $856万
 $16,389/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40457,7 +40457,7 @@
           <t>D | 518呎 (2房)
 $875万
 $16,884/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -40465,7 +40465,7 @@
           <t>E | 437呎 (1房)
 $716万
 $16,389/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -40473,7 +40473,7 @@
           <t>F | 418呎 (1房)
 $684万
 $16,356/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -40489,7 +40489,7 @@
           <t>H | 573呎 (2房)
 $1043万
 $18,195/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -40520,7 +40520,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,908/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -40528,7 +40528,7 @@
           <t>D | 518呎 (2房)
 $871万
 $16,817/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -40536,7 +40536,7 @@
           <t>E | 437呎 (1房)
 $713万
 $16,323/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -40544,7 +40544,7 @@
           <t>F | 418呎 (1房)
 $681万
 $16,289/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -40560,7 +40560,7 @@
           <t>H | 573呎 (2房)
 $1074万
 $18,743/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40591,7 +40591,7 @@
           <t>C | 522呎 (2房)
 $859万
 $16,452/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -40599,7 +40599,7 @@
           <t>D | 518呎 (2房)
 $868万
 $16,749/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -40607,7 +40607,7 @@
           <t>E | 437呎 (1房)
 $710万
 $16,259/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -40615,7 +40615,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,799/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -40631,7 +40631,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,651/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40662,7 +40662,7 @@
           <t>C | 522呎 (2房)
 $857万
 $16,420/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -40670,7 +40670,7 @@
           <t>D | 518呎 (2房)
 $866万
 $16,716/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -40678,7 +40678,7 @@
           <t>E | 437呎 (1房)
 $709万
 $16,227/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -40686,7 +40686,7 @@
           <t>F | 418呎 (1房)
 $677万
 $16,194/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -40694,7 +40694,7 @@
           <t>G | 538呎 (2房)
 $1015万
 $18,872/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -40702,7 +40702,7 @@
           <t>H | 573呎 (2房)
 $1030万
 $17,970/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
           <t>C | 522呎 (2房)
 $852万
 $16,322/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -40741,7 +40741,7 @@
           <t>D | 518呎 (2房)
 $861万
 $16,616/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -40749,7 +40749,7 @@
           <t>E | 437呎 (1房)
 $705万
 $16,128/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -40757,7 +40757,7 @@
           <t>F | 418呎 (1房)
 $673万
 $16,098/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -40765,7 +40765,7 @@
           <t>G | 538呎 (2房)
 $1008万
 $18,732/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -40773,7 +40773,7 @@
           <t>H | 573呎 (2房)
 $1022万
 $17,836/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -40804,7 +40804,7 @@
           <t>C | 522呎 (2房)
 $849万
 $16,257/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -40812,7 +40812,7 @@
           <t>D | 518呎 (2房)
 $857万
 $16,550/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -40820,7 +40820,7 @@
           <t>E | 437呎 (1房)
 $702万
 $16,064/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -40828,7 +40828,7 @@
           <t>F | 418呎 (1房)
 $670万
 $16,033/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -40836,7 +40836,7 @@
           <t>G | 538呎 (2房)
 $1003万
 $18,638/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -40844,7 +40844,7 @@
           <t>H | 573呎 (2房)
 $1017万
 $17,747/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -40875,7 +40875,7 @@
           <t>C | 522呎 (2房)
 $845万
 $16,192/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -40883,7 +40883,7 @@
           <t>D | 518呎 (2房)
 $854万
 $16,485/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -40891,7 +40891,7 @@
           <t>E | 437呎 (1房)
 $699万
 $16,000/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -40899,7 +40899,7 @@
           <t>F | 418呎 (1房)
 $668万
 $15,969/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -40915,7 +40915,7 @@
           <t>H | 573呎 (2房)
 $1012万
 $17,658/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -40946,7 +40946,7 @@
           <t>C | 522呎 (2房)
 $842万
 $16,128/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -40954,7 +40954,7 @@
           <t>D | 518呎 (2房)
 $850万
 $16,419/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -40962,7 +40962,7 @@
           <t>E | 437呎 (1房)
 $696万
 $15,938/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -40970,7 +40970,7 @@
           <t>F | 418呎 (1房)
 $665万
 $15,907/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -40986,7 +40986,7 @@
           <t>H | 573呎 (2房)
 $1007万
 $17,571/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
           <t>C | 522呎 (2房)
 $838万
 $16,063/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -41025,7 +41025,7 @@
           <t>D | 518呎 (2房)
 $847万
 $16,353/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -41033,7 +41033,7 @@
           <t>E | 437呎 (1房)
 $694万
 $15,874/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -41041,7 +41041,7 @@
           <t>F | 418呎 (1房)
 $686万
 $16,402/呎
-(25年-10月-22日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -41049,7 +41049,7 @@
           <t>G | 538呎 (2房)
 $988万
 $18,362/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -41057,7 +41057,7 @@
           <t>H | 573呎 (2房)
 $1002万
 $17,483/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -41088,7 +41088,7 @@
           <t>C | 522呎 (2房)
 $835万
 $15,992/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -41096,7 +41096,7 @@
           <t>D | 518呎 (2房)
 $843万
 $16,280/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -41104,7 +41104,7 @@
           <t>E | 437呎 (1房)
 $690万
 $15,801/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -41112,7 +41112,7 @@
           <t>F | 418呎 (1房)
 $659万
 $15,773/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -41120,7 +41120,7 @@
           <t>G | 538呎 (2房)
 $983万
 $18,270/呎
-(26年-07月-11日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -41128,7 +41128,7 @@
           <t>H | 573呎 (2房)
 $997万
 $17,396/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -41159,7 +41159,7 @@
           <t>C | 522呎 (2房)
 $831万
 $15,920/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -41167,7 +41167,7 @@
           <t>D | 518呎 (2房)
 $840万
 $16,207/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -41175,7 +41175,7 @@
           <t>E | 437呎 (1房)
 $688万
 $15,732/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -41183,7 +41183,7 @@
           <t>F | 418呎 (1房)
 $656万
 $15,701/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -41191,7 +41191,7 @@
           <t>G | 538呎 (2房)
 $978万
 $18,180/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -41199,7 +41199,7 @@
           <t>H | 573呎 (2房)
 $992万
 $17,311/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -41230,7 +41230,7 @@
           <t>C | 522呎 (2房)
 $827万
 $15,841/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -41238,7 +41238,7 @@
           <t>D | 518呎 (2房)
 $835万
 $16,125/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -41246,7 +41246,7 @@
           <t>E | 437呎 (1房)
 $684万
 $15,654/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -41254,7 +41254,7 @@
           <t>F | 418呎 (1房)
 $653万
 $15,624/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -41262,7 +41262,7 @@
           <t>G | 538呎 (2房)
 $973万
 $18,089/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -41270,7 +41270,7 @@
           <t>H | 573呎 (2房)
 $987万
 $17,223/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -41301,7 +41301,7 @@
           <t>C | 522呎 (2房)
 $815万
 $15,615/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -41309,7 +41309,7 @@
           <t>D | 518呎 (2房)
 $833万
 $16,087/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -41317,7 +41317,7 @@
           <t>E | 437呎 (1房)
 $682万
 $15,616/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -41325,7 +41325,7 @@
           <t>F | 418呎 (1房)
 $674万
 $16,132/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -41333,7 +41333,7 @@
           <t>G | 538呎 (2房)
 $971万
 $18,045/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -41341,7 +41341,7 @@
           <t>H | 573呎 (2房)
 $973万
 $16,979/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -41372,7 +41372,7 @@
           <t>C | 522呎 (2房)
 $819万
 $15,684/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -41380,7 +41380,7 @@
           <t>D | 518呎 (2房)
 $827万
 $15,967/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -41388,7 +41388,7 @@
           <t>E | 437呎 (1房)
 $677万
 $15,499/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -41396,7 +41396,7 @@
           <t>F | 418呎 (1房)
 $639万
 $15,285/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -41404,7 +41404,7 @@
           <t>G | 538呎 (2房)
 $964万
 $17,911/呎
-(26年-07月-11日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -41412,7 +41412,7 @@
           <t>H | 573呎 (2房)
 $966万
 $16,853/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -41443,7 +41443,7 @@
           <t>C | 522呎 (2房)
 $805万
 $15,423/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -41451,7 +41451,7 @@
           <t>D | 518呎 (2房)
 $823万
 $15,888/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -41459,7 +41459,7 @@
           <t>E | 437呎 (1房)
 $674万
 $15,421/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -41467,7 +41467,7 @@
           <t>F | 418呎 (1房)
 $643万
 $15,392/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -41475,7 +41475,7 @@
           <t>G | 538呎 (2房)
 $959万
 $17,820/呎
-(26年-07月-11日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -41483,7 +41483,7 @@
           <t>H | 573呎 (2房)
 $972万
 $16,967/呎
-(26年-04月-25日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -41514,7 +41514,7 @@
           <t>C | 522呎 (2房)
 $811万
 $15,529/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -41522,7 +41522,7 @@
           <t>D | 518呎 (2房)
 $819万
 $15,807/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -41530,7 +41530,7 @@
           <t>E | 437呎 (1房)
 $671万
 $15,346/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -41538,7 +41538,7 @@
           <t>F | 418呎 (1房)
 $633万
 $15,148/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -41546,7 +41546,7 @@
           <t>G | 538呎 (2房)
 $954万
 $17,732/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -41554,7 +41554,7 @@
           <t>H | 573呎 (2房)
 $968万
 $16,885/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -41803,7 +41803,7 @@
           <t>C | 547呎 (2房)
 $1039万
 $18,987/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -41835,7 +41835,7 @@
           <t>G | 554呎 (2房)
 $1175万
 $21,215/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -41874,7 +41874,7 @@
           <t>C | 547呎 (2房)
 $1023万
 $18,707/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -41882,7 +41882,7 @@
           <t>D | 538呎 (2房)
 $994万
 $18,485/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -41906,7 +41906,7 @@
           <t>G | 554呎 (2房)
 $1158万
 $20,903/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -41945,7 +41945,7 @@
           <t>C | 547呎 (2房)
 $1008万
 $18,431/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -41977,7 +41977,7 @@
           <t>G | 554呎 (2房)
 $1141万
 $20,592/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -42016,7 +42016,7 @@
           <t>C | 547呎 (2房)
 $996万
 $18,212/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -42048,7 +42048,7 @@
           <t>G | 554呎 (2房)
 $1127万
 $20,348/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -42087,7 +42087,7 @@
           <t>C | 547呎 (2房)
 $984万
 $17,996/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -42119,7 +42119,7 @@
           <t>G | 554呎 (2房)
 $1114万
 $20,106/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -42158,7 +42158,7 @@
           <t>C | 547呎 (2房)
 $977万
 $17,854/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -42166,7 +42166,7 @@
           <t>D | 538呎 (2房)
 $976万
 $18,139/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -42190,7 +42190,7 @@
           <t>G | 554呎 (2房)
 $1103万
 $19,908/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -42229,7 +42229,7 @@
           <t>C | 547呎 (2房)
 $973万
 $17,782/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -42237,7 +42237,7 @@
           <t>D | 538呎 (2房)
 $955万
 $17,747/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -42253,7 +42253,7 @@
           <t>F | 512呎 (2房)
 $893万
 $17,436/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -42261,7 +42261,7 @@
           <t>G | 554呎 (2房)
 $1097万
 $19,809/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -42300,7 +42300,7 @@
           <t>C | 547呎 (2房)
 $967万
 $17,676/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -42308,7 +42308,7 @@
           <t>D | 538呎 (2房)
 $949万
 $17,641/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -42324,7 +42324,7 @@
           <t>F | 512呎 (2房)
 $887万
 $17,330/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -42332,7 +42332,7 @@
           <t>G | 554呎 (2房)
 $1084万
 $19,574/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -42371,7 +42371,7 @@
           <t>C | 547呎 (2房)
 $963万
 $17,607/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -42379,7 +42379,7 @@
           <t>D | 538呎 (2房)
 $945万
 $17,572/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -42395,7 +42395,7 @@
           <t>F | 512呎 (2房)
 $884万
 $17,262/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -42403,7 +42403,7 @@
           <t>G | 554呎 (2房)
 $1076万
 $19,419/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -42411,7 +42411,7 @@
           <t>H | 573呎 (2房)
 $1197万
 $20,883/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -42442,7 +42442,7 @@
           <t>C | 547呎 (2房)
 $959万
 $17,536/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -42450,7 +42450,7 @@
           <t>D | 538呎 (2房)
 $942万
 $17,500/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -42466,7 +42466,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,193/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -42474,7 +42474,7 @@
           <t>G | 554呎 (2房)
 $1067万
 $19,265/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -42513,7 +42513,7 @@
           <t>C | 547呎 (2房)
 $955万
 $17,466/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -42521,7 +42521,7 @@
           <t>D | 538呎 (2房)
 $938万
 $17,431/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -42537,7 +42537,7 @@
           <t>F | 512呎 (2房)
 $877万
 $17,125/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -42545,7 +42545,7 @@
           <t>G | 554呎 (2房)
 $1059万
 $19,112/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -42584,7 +42584,7 @@
           <t>C | 547呎 (2房)
 $952万
 $17,397/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -42592,7 +42592,7 @@
           <t>D | 538呎 (2房)
 $934万
 $17,362/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -42616,7 +42616,7 @@
           <t>G | 554呎 (2房)
 $1050万
 $18,958/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -42655,7 +42655,7 @@
           <t>C | 547呎 (2房)
 $937万
 $17,122/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -42663,7 +42663,7 @@
           <t>D | 538呎 (2房)
 $930万
 $17,294/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -42687,7 +42687,7 @@
           <t>G | 554呎 (2房)
 $1042万
 $18,809/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -42695,7 +42695,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,229/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
           <t>C | 547呎 (2房)
 $944万
 $17,258/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -42734,7 +42734,7 @@
           <t>D | 538呎 (2房)
 $927万
 $17,225/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -42758,7 +42758,7 @@
           <t>G | 554呎 (2房)
 $1034万
 $18,661/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -42797,7 +42797,7 @@
           <t>C | 547呎 (2房)
 $940万
 $17,190/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -42805,7 +42805,7 @@
           <t>D | 538呎 (2房)
 $923万
 $17,154/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -42821,7 +42821,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,191/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -42829,7 +42829,7 @@
           <t>G | 554呎 (2房)
 $1026万
 $18,511/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -42868,7 +42868,7 @@
           <t>C | 547呎 (2房)
 $938万
 $17,155/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -42876,7 +42876,7 @@
           <t>D | 538呎 (2房)
 $921万
 $17,121/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -42892,7 +42892,7 @@
           <t>F | 512呎 (2房)
 $878万
 $17,156/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -42900,7 +42900,7 @@
           <t>G | 554呎 (2房)
 $1022万
 $18,451/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -42939,7 +42939,7 @@
           <t>C | 547呎 (2房)
 $933万
 $17,053/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -42947,7 +42947,7 @@
           <t>D | 538呎 (2房)
 $905万
 $16,818/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -42963,7 +42963,7 @@
           <t>F | 512呎 (2房)
 $856万
 $16,719/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -42971,7 +42971,7 @@
           <t>G | 554呎 (2房)
 $1012万
 $18,274/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -42979,7 +42979,7 @@
           <t>H | 573呎 (2房)
 $1126万
 $19,653/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -43010,7 +43010,7 @@
           <t>C | 547呎 (2房)
 $902万
 $16,484/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -43018,7 +43018,7 @@
           <t>D | 538呎 (2房)
 $912万
 $16,952/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43034,7 +43034,7 @@
           <t>F | 512呎 (2房)
 $853万
 $16,652/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -43042,7 +43042,7 @@
           <t>G | 554呎 (2房)
 $996万
 $17,969/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -43081,7 +43081,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,718/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -43089,7 +43089,7 @@
           <t>D | 538呎 (2房)
 $908万
 $16,885/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43105,7 +43105,7 @@
           <t>F | 512呎 (2房)
 $849万
 $16,586/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -43113,7 +43113,7 @@
           <t>G | 554呎 (2房)
 $1002万
 $18,092/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -43152,7 +43152,7 @@
           <t>C | 547呎 (2房)
 $922万
 $16,850/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -43160,7 +43160,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,619/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -43168,7 +43168,7 @@
           <t>E | 537呎 (2房)
 $907万
 $16,885/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -43176,7 +43176,7 @@
           <t>F | 512呎 (2房)
 $846万
 $16,520/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -43184,7 +43184,7 @@
           <t>G | 554呎 (2房)
 $986万
 $17,791/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -43223,7 +43223,7 @@
           <t>C | 547呎 (2房)
 $918万
 $16,782/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -43231,7 +43231,7 @@
           <t>D | 538呎 (2房)
 $901万
 $16,751/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -43247,7 +43247,7 @@
           <t>F | 512呎 (2房)
 $842万
 $16,453/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -43255,7 +43255,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,913/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -43294,7 +43294,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,715/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -43302,7 +43302,7 @@
           <t>D | 538呎 (2房)
 $887万
 $16,487/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -43318,7 +43318,7 @@
           <t>F | 512呎 (2房)
 $839万
 $16,389/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -43326,7 +43326,7 @@
           <t>G | 554呎 (2房)
 $987万
 $17,823/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -43365,7 +43365,7 @@
           <t>C | 547呎 (2房)
 $911万
 $16,649/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -43373,7 +43373,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,615/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -43381,7 +43381,7 @@
           <t>E | 537呎 (2房)
 $878万
 $16,356/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -43389,7 +43389,7 @@
           <t>F | 512呎 (2房)
 $836万
 $16,324/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -43397,7 +43397,7 @@
           <t>G | 554呎 (2房)
 $982万
 $17,735/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -43436,7 +43436,7 @@
           <t>C | 547呎 (2房)
 $907万
 $16,581/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -43444,7 +43444,7 @@
           <t>D | 538呎 (2房)
 $922万
 $17,134/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -43452,7 +43452,7 @@
           <t>E | 537呎 (2房)
 $875万
 $16,291/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -43460,7 +43460,7 @@
           <t>F | 512呎 (2房)
 $832万
 $16,258/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -43468,7 +43468,7 @@
           <t>G | 554呎 (2房)
 $978万
 $17,648/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -43507,7 +43507,7 @@
           <t>C | 547呎 (2房)
 $905万
 $16,550/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -43515,7 +43515,7 @@
           <t>D | 538呎 (2房)
 $889万
 $16,517/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -43523,7 +43523,7 @@
           <t>E | 537呎 (2房)
 $873万
 $16,259/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -43531,7 +43531,7 @@
           <t>F | 512呎 (2房)
 $831万
 $16,227/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -43539,7 +43539,7 @@
           <t>G | 554呎 (2房)
 $964万
 $17,395/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -43578,7 +43578,7 @@
           <t>C | 547呎 (2房)
 $900万
 $16,452/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -43586,7 +43586,7 @@
           <t>D | 538呎 (2房)
 $883万
 $16,418/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -43594,7 +43594,7 @@
           <t>E | 537呎 (2房)
 $868万
 $16,162/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -43602,7 +43602,7 @@
           <t>F | 512呎 (2房)
 $826万
 $16,131/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -43610,7 +43610,7 @@
           <t>G | 554呎 (2房)
 $968万
 $17,471/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -43649,7 +43649,7 @@
           <t>C | 547呎 (2房)
 $896万
 $16,384/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -43657,7 +43657,7 @@
           <t>D | 538呎 (2房)
 $870万
 $16,162/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -43665,7 +43665,7 @@
           <t>E | 537呎 (2房)
 $864万
 $16,099/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -43673,7 +43673,7 @@
           <t>F | 512呎 (2房)
 $822万
 $16,064/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -43681,7 +43681,7 @@
           <t>G | 554呎 (2房)
 $963万
 $17,384/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -43720,7 +43720,7 @@
           <t>C | 547呎 (2房)
 $893万
 $16,320/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -43728,7 +43728,7 @@
           <t>D | 538呎 (2房)
 $876万
 $16,288/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -43736,7 +43736,7 @@
           <t>E | 537呎 (2房)
 $861万
 $16,034/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -43744,7 +43744,7 @@
           <t>F | 512呎 (2房)
 $819万
 $16,000/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -43752,7 +43752,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,908/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -43760,7 +43760,7 @@
           <t>H | 573呎 (2房)
 $1066万
 $18,604/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -43791,7 +43791,7 @@
           <t>C | 547呎 (2房)
 $889万
 $16,256/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -43799,7 +43799,7 @@
           <t>D | 538呎 (2房)
 $873万
 $16,223/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -43807,7 +43807,7 @@
           <t>E | 537呎 (2房)
 $858万
 $15,970/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -43815,7 +43815,7 @@
           <t>F | 512呎 (2房)
 $816万
 $15,938/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -43823,7 +43823,7 @@
           <t>G | 554呎 (2房)
 $954万
 $17,211/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -43862,7 +43862,7 @@
           <t>C | 547呎 (2房)
 $886万
 $16,190/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -43870,7 +43870,7 @@
           <t>D | 538呎 (2房)
 $869万
 $16,158/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -43878,7 +43878,7 @@
           <t>E | 537呎 (2房)
 $854万
 $15,907/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -43886,7 +43886,7 @@
           <t>F | 512呎 (2房)
 $813万
 $15,875/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -43894,7 +43894,7 @@
           <t>G | 554呎 (2房)
 $949万
 $17,128/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -43902,7 +43902,7 @@
           <t>H | 573呎 (2房)
 $1045万
 $18,237/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -43933,7 +43933,7 @@
           <t>C | 547呎 (2房)
 $882万
 $16,117/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -43941,7 +43941,7 @@
           <t>D | 538呎 (2房)
 $866万
 $16,087/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -43949,7 +43949,7 @@
           <t>E | 537呎 (2房)
 $850万
 $15,834/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -43957,7 +43957,7 @@
           <t>F | 512呎 (2房)
 $809万
 $15,803/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -43965,7 +43965,7 @@
           <t>G | 554呎 (2房)
 $944万
 $17,042/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -43973,7 +43973,7 @@
           <t>H | 573呎 (2房)
 $1040万
 $18,147/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44004,7 +44004,7 @@
           <t>C | 547呎 (2房)
 $878万
 $16,046/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -44012,7 +44012,7 @@
           <t>D | 538呎 (2房)
 $862万
 $16,015/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -44020,7 +44020,7 @@
           <t>E | 537呎 (2房)
 $846万
 $15,764/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -44028,7 +44028,7 @@
           <t>F | 512呎 (2房)
 $834万
 $16,287/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -44036,7 +44036,7 @@
           <t>G | 554呎 (2房)
 $939万
 $16,957/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -44044,7 +44044,7 @@
           <t>H | 573呎 (2房)
 $1035万
 $18,056/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44075,7 +44075,7 @@
           <t>C | 547呎 (2房)
 $873万
 $15,965/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -44083,7 +44083,7 @@
           <t>D | 538呎 (2房)
 $888万
 $16,498/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -44091,7 +44091,7 @@
           <t>E | 537呎 (2房)
 $859万
 $15,998/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -44099,7 +44099,7 @@
           <t>F | 512呎 (2房)
 $802万
 $15,654/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -44107,7 +44107,7 @@
           <t>G | 554呎 (2房)
 $924万
 $16,673/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -44115,7 +44115,7 @@
           <t>H | 573呎 (2房)
 $1029万
 $17,965/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44146,7 @@
           <t>C | 547呎 (2房)
 $872万
 $15,934/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -44154,7 +44154,7 @@
           <t>D | 538呎 (2房)
 $886万
 $16,463/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -44162,7 +44162,7 @@
           <t>E | 537呎 (2房)
 $857万
 $15,966/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -44170,7 +44170,7 @@
           <t>F | 512呎 (2房)
 $790万
 $15,438/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -44178,7 +44178,7 @@
           <t>G | 554呎 (2房)
 $932万
 $16,830/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -44186,7 +44186,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,921/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
           <t>C | 547呎 (2房)
 $866万
 $15,839/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -44225,7 +44225,7 @@
           <t>D | 538呎 (2房)
 $850万
 $15,807/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -44233,7 +44233,7 @@
           <t>E | 537呎 (2房)
 $852万
 $15,872/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -44241,7 +44241,7 @@
           <t>F | 512呎 (2房)
 $795万
 $15,529/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -44249,7 +44249,7 @@
           <t>G | 554呎 (2房)
 $926万
 $16,706/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -44257,7 +44257,7 @@
           <t>H | 573呎 (2房)
 $1019万
 $17,787/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
           <t>C | 547呎 (2房)
 $862万
 $15,761/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -44296,7 +44296,7 @@
           <t>D | 538呎 (2房)
 $846万
 $15,730/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -44304,7 +44304,7 @@
           <t>E | 537呎 (2房)
 $848万
 $15,791/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -44312,7 +44312,7 @@
           <t>F | 512呎 (2房)
 $791万
 $15,453/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -44320,7 +44320,7 @@
           <t>G | 554呎 (2房)
 $921万
 $16,623/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I40" s="21" t="inlineStr">
@@ -44328,7 +44328,7 @@
           <t>H | 573呎 (2房)
 $1014万
 $17,698/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44359,7 +44359,7 @@
           <t>C | 547呎 (2房)
 $858万
 $15,682/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -44367,7 +44367,7 @@
           <t>D | 538呎 (2房)
 $842万
 $15,651/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -44375,7 +44375,7 @@
           <t>E | 537呎 (2房)
 $844万
 $15,715/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
@@ -44383,7 +44383,7 @@
           <t>F | 512呎 (2房)
 $788万
 $15,398/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
@@ -44391,7 +44391,7 @@
           <t>G | 554呎 (2房)
 $916万
 $16,540/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -44399,7 +44399,7 @@
           <t>H | 573呎 (2房)
 $1009万
 $17,611/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-柴湾-海德园第1期.xlsx
+++ b/files/港岛-柴湾-海德园第1期.xlsx
@@ -39100,7 +39100,7 @@
           <t>C | 522呎 (2房)
 $940万
 $18,000/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39116,7 +39116,7 @@
           <t>E | 437呎 (1房)
 $777万
 $17,785/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -39124,7 +39124,7 @@
           <t>F | 418呎 (1房)
 $742万
 $17,751/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -39140,7 +39140,7 @@
           <t>H | 571呎 (2房)
 $1236万
 $21,651/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -39171,7 +39171,7 @@
           <t>C | 522呎 (2房)
 $933万
 $17,874/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -39179,7 +39179,7 @@
           <t>D | 518呎 (2房)
 $943万
 $18,197/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -39187,7 +39187,7 @@
           <t>E | 437呎 (1房)
 $772万
 $17,664/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -39195,7 +39195,7 @@
           <t>F | 418呎 (1房)
 $737万
 $17,627/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -39211,7 +39211,7 @@
           <t>H | 573呎 (2房)
 $1215万
 $21,208/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -39242,7 +39242,7 @@
           <t>C | 522呎 (2房)
 $926万
 $17,749/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39258,7 +39258,7 @@
           <t>E | 437呎 (1房)
 $766万
 $17,538/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -39266,7 +39266,7 @@
           <t>F | 418呎 (1房)
 $732万
 $17,505/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -39274,7 +39274,7 @@
           <t>G | 538呎 (2房)
 $1160万
 $21,556/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -39282,7 +39282,7 @@
           <t>H | 573呎 (2房)
 $1190万
 $20,771/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -39313,7 +39313,7 @@
           <t>C | 522呎 (2房)
 $923万
 $17,678/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -39321,7 +39321,7 @@
           <t>D | 518呎 (2房)
 $932万
 $17,998/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -39329,7 +39329,7 @@
           <t>E | 437呎 (1房)
 $764万
 $17,471/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -39337,7 +39337,7 @@
           <t>F | 418呎 (1房)
 $729万
 $17,435/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -39353,7 +39353,7 @@
           <t>H | 573呎 (2房)
 $1172万
 $20,445/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -39384,7 +39384,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -39392,7 +39392,7 @@
           <t>D | 518呎 (2房)
 $930万
 $17,961/呎
-(26年-07月)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -39400,7 +39400,7 @@
           <t>E | 437呎 (1房)
 $762万
 $17,435/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -39408,7 +39408,7 @@
           <t>F | 418呎 (1房)
 $753万
 $18,014/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -39416,7 +39416,7 @@
           <t>G | 538呎 (2房)
 $1143万
 $21,238/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -39424,7 +39424,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,222/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -39455,7 +39455,7 @@
           <t>C | 522呎 (2房)
 $916万
 $17,538/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -39463,7 +39463,7 @@
           <t>D | 518呎 (2房)
 $925万
 $17,853/呎
-(26年-07月)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -39471,7 +39471,7 @@
           <t>E | 437呎 (1房)
 $757万
 $17,332/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -39479,7 +39479,7 @@
           <t>F | 418呎 (1房)
 $723万
 $17,297/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -39487,7 +39487,7 @@
           <t>G | 538呎 (2房)
 $1129万
 $20,987/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -39495,7 +39495,7 @@
           <t>H | 573呎 (2房)
 $1145万
 $19,983/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -39526,7 +39526,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,264/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -39534,7 +39534,7 @@
           <t>D | 518呎 (2房)
 $921万
 $17,782/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -39542,7 +39542,7 @@
           <t>E | 437呎 (1房)
 $754万
 $17,263/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>F | 418呎 (1房)
 $720万
 $17,227/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>G | 538呎 (2房)
 $1120万
 $20,818/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -39566,7 +39566,7 @@
           <t>H | 573呎 (2房)
 $1136万
 $19,824/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39597,7 @@
           <t>C | 522呎 (2房)
 $908万
 $17,398/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>D | 518呎 (2房)
 $918万
 $17,712/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>E | 437呎 (1房)
 $751万
 $17,192/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>F | 418呎 (1房)
 $717万
 $17,158/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>H | 573呎 (2房)
 $1127万
 $19,665/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -39668,7 +39668,7 @@
           <t>C | 522呎 (2房)
 $905万
 $17,330/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 518呎 (2房)
 $914万
 $17,641/呎
-(26年-06月)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 437呎 (1房)
 $748万
 $17,124/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 418呎 (1房)
 $714万
 $17,089/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -39708,7 +39708,7 @@
           <t>H | 573呎 (2房)
 $1118万
 $19,510/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -39739,7 +39739,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,261/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>D | 518呎 (2房)
 $910万
 $17,571/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -39755,7 +39755,7 @@
           <t>E | 437呎 (1房)
 $745万
 $17,057/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -39763,7 +39763,7 @@
           <t>F | 418呎 (1房)
 $712万
 $17,022/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -39779,7 +39779,7 @@
           <t>H | 573呎 (2房)
 $1109万
 $19,354/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39810,7 @@
           <t>C | 522呎 (2房)
 $897万
 $17,192/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -39818,7 +39818,7 @@
           <t>D | 518呎 (2房)
 $906万
 $17,500/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -39826,7 +39826,7 @@
           <t>E | 437呎 (1房)
 $742万
 $16,989/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -39834,7 +39834,7 @@
           <t>F | 418呎 (1房)
 $709万
 $16,955/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -39850,7 +39850,7 @@
           <t>H | 573呎 (2房)
 $1100万
 $19,201/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -39881,7 +39881,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -39889,7 +39889,7 @@
           <t>D | 518呎 (2房)
 $903万
 $17,432/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -39897,7 +39897,7 @@
           <t>E | 437呎 (1房)
 $739万
 $16,920/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -39905,7 +39905,7 @@
           <t>F | 418呎 (1房)
 $706万
 $16,885/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -39913,7 +39913,7 @@
           <t>G | 538呎 (2房)
 $1076万
 $20,007/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -39921,7 +39921,7 @@
           <t>H | 573呎 (2房)
 $1092万
 $19,049/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -39952,7 +39952,7 @@
           <t>C | 522呎 (2房)
 $890万
 $17,056/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -39960,7 +39960,7 @@
           <t>D | 518呎 (2房)
 $899万
 $17,363/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -39968,7 +39968,7 @@
           <t>E | 437呎 (1房)
 $736万
 $16,854/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -39976,7 +39976,7 @@
           <t>F | 418呎 (1房)
 $703万
 $16,818/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -39992,7 +39992,7 @@
           <t>H | 573呎 (2房)
 $1083万
 $18,897/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -40023,7 +40023,7 @@
           <t>C | 522呎 (2房)
 $888万
 $17,021/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -40039,7 +40039,7 @@
           <t>E | 437呎 (1房)
 $735万
 $16,819/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -40047,7 +40047,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,787/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -40055,7 +40055,7 @@
           <t>G | 538呎 (2房)
 $1064万
 $19,783/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -40063,7 +40063,7 @@
           <t>H | 573呎 (2房)
 $1079万
 $18,836/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -40094,7 +40094,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,920/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -40102,7 +40102,7 @@
           <t>D | 518呎 (2房)
 $892万
 $17,224/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -40110,7 +40110,7 @@
           <t>E | 437呎 (1房)
 $731万
 $16,721/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -40118,7 +40118,7 @@
           <t>F | 418呎 (1房)
 $698万
 $16,687/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -40134,7 +40134,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,654/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -40165,7 +40165,7 @@
           <t>C | 522呎 (2房)
 $880万
 $16,852/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -40173,7 +40173,7 @@
           <t>D | 518呎 (2房)
 $889万
 $17,156/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -40181,7 +40181,7 @@
           <t>E | 437呎 (1房)
 $728万
 $16,652/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -40189,7 +40189,7 @@
           <t>F | 418呎 (1房)
 $719万
 $17,206/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -40205,7 +40205,7 @@
           <t>H | 573呎 (2房)
 $1064万
 $18,562/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40236,7 @@
           <t>C | 522呎 (2房)
 $876万
 $16,785/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -40244,7 +40244,7 @@
           <t>D | 518呎 (2房)
 $885万
 $17,087/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40252,7 +40252,7 @@
           <t>E | 437呎 (1房)
 $725万
 $16,586/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -40260,7 +40260,7 @@
           <t>F | 418呎 (1房)
 $692万
 $16,553/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -40276,7 +40276,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,925/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
     </row>
@@ -40307,7 +40307,7 @@
           <t>C | 522呎 (2房)
 $873万
 $16,718/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -40315,7 +40315,7 @@
           <t>D | 518呎 (2房)
 $882万
 $17,019/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40323,7 +40323,7 @@
           <t>E | 437呎 (1房)
 $722万
 $16,519/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -40331,7 +40331,7 @@
           <t>F | 418呎 (1房)
 $689万
 $16,488/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -40347,7 +40347,7 @@
           <t>H | 573呎 (2房)
 $1053万
 $18,379/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
     </row>
@@ -40378,7 +40378,7 @@
           <t>C | 522呎 (2房)
 $869万
 $16,651/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -40386,7 +40386,7 @@
           <t>D | 518呎 (2房)
 $878万
 $16,952/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -40394,7 +40394,7 @@
           <t>E | 437呎 (1房)
 $719万
 $16,455/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -40402,7 +40402,7 @@
           <t>F | 418呎 (1房)
 $711万
 $17,002/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -40418,7 +40418,7 @@
           <t>H | 573呎 (2房)
 $1048万
 $18,286/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -40449,7 +40449,7 @@
           <t>C | 522呎 (2房)
 $856万
 $16,389/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40457,7 +40457,7 @@
           <t>D | 518呎 (2房)
 $875万
 $16,884/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -40465,7 +40465,7 @@
           <t>E | 437呎 (1房)
 $716万
 $16,389/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -40473,7 +40473,7 @@
           <t>F | 418呎 (1房)
 $684万
 $16,356/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -40489,7 +40489,7 @@
           <t>H | 573呎 (2房)
 $1043万
 $18,195/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -40520,7 +40520,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,908/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -40528,7 +40528,7 @@
           <t>D | 518呎 (2房)
 $871万
 $16,817/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -40536,7 +40536,7 @@
           <t>E | 437呎 (1房)
 $713万
 $16,323/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -40544,7 +40544,7 @@
           <t>F | 418呎 (1房)
 $681万
 $16,289/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -40560,7 +40560,7 @@
           <t>H | 573呎 (2房)
 $1074万
 $18,743/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -40591,7 +40591,7 @@
           <t>C | 522呎 (2房)
 $859万
 $16,452/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -40599,7 +40599,7 @@
           <t>D | 518呎 (2房)
 $868万
 $16,749/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -40607,7 +40607,7 @@
           <t>E | 437呎 (1房)
 $710万
 $16,259/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -40615,7 +40615,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,799/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -40631,7 +40631,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,651/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -40662,7 +40662,7 @@
           <t>C | 522呎 (2房)
 $857万
 $16,420/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -40670,7 +40670,7 @@
           <t>D | 518呎 (2房)
 $866万
 $16,716/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -40678,7 +40678,7 @@
           <t>E | 437呎 (1房)
 $709万
 $16,227/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -40686,7 +40686,7 @@
           <t>F | 418呎 (1房)
 $677万
 $16,194/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -40694,7 +40694,7 @@
           <t>G | 538呎 (2房)
 $1015万
 $18,872/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -40702,7 +40702,7 @@
           <t>H | 573呎 (2房)
 $1030万
 $17,970/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
           <t>C | 522呎 (2房)
 $852万
 $16,322/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -40741,7 +40741,7 @@
           <t>D | 518呎 (2房)
 $861万
 $16,616/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -40749,7 +40749,7 @@
           <t>E | 437呎 (1房)
 $705万
 $16,128/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -40757,7 +40757,7 @@
           <t>F | 418呎 (1房)
 $673万
 $16,098/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -40765,7 +40765,7 @@
           <t>G | 538呎 (2房)
 $1008万
 $18,732/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -40773,7 +40773,7 @@
           <t>H | 573呎 (2房)
 $1022万
 $17,836/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -40804,7 +40804,7 @@
           <t>C | 522呎 (2房)
 $849万
 $16,257/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -40812,7 +40812,7 @@
           <t>D | 518呎 (2房)
 $857万
 $16,550/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -40820,7 +40820,7 @@
           <t>E | 437呎 (1房)
 $702万
 $16,064/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -40828,7 +40828,7 @@
           <t>F | 418呎 (1房)
 $670万
 $16,033/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -40836,7 +40836,7 @@
           <t>G | 538呎 (2房)
 $1003万
 $18,638/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -40844,7 +40844,7 @@
           <t>H | 573呎 (2房)
 $1017万
 $17,747/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -40875,7 +40875,7 @@
           <t>C | 522呎 (2房)
 $845万
 $16,192/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -40883,7 +40883,7 @@
           <t>D | 518呎 (2房)
 $854万
 $16,485/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -40891,7 +40891,7 @@
           <t>E | 437呎 (1房)
 $699万
 $16,000/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -40899,7 +40899,7 @@
           <t>F | 418呎 (1房)
 $668万
 $15,969/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -40915,7 +40915,7 @@
           <t>H | 573呎 (2房)
 $1012万
 $17,658/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -40946,7 +40946,7 @@
           <t>C | 522呎 (2房)
 $842万
 $16,128/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -40954,7 +40954,7 @@
           <t>D | 518呎 (2房)
 $850万
 $16,419/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -40962,7 +40962,7 @@
           <t>E | 437呎 (1房)
 $696万
 $15,938/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -40970,7 +40970,7 @@
           <t>F | 418呎 (1房)
 $665万
 $15,907/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -40986,7 +40986,7 @@
           <t>H | 573呎 (2房)
 $1007万
 $17,571/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -41017,7 +41017,7 @@
           <t>C | 522呎 (2房)
 $838万
 $16,063/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -41025,7 +41025,7 @@
           <t>D | 518呎 (2房)
 $847万
 $16,353/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -41033,7 +41033,7 @@
           <t>E | 437呎 (1房)
 $694万
 $15,874/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -41041,7 +41041,7 @@
           <t>F | 418呎 (1房)
 $686万
 $16,402/呎
-(25年-10月)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -41049,7 +41049,7 @@
           <t>G | 538呎 (2房)
 $988万
 $18,362/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -41057,7 +41057,7 @@
           <t>H | 573呎 (2房)
 $1002万
 $17,483/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -41088,7 +41088,7 @@
           <t>C | 522呎 (2房)
 $835万
 $15,992/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -41096,7 +41096,7 @@
           <t>D | 518呎 (2房)
 $843万
 $16,280/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -41104,7 +41104,7 @@
           <t>E | 437呎 (1房)
 $690万
 $15,801/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -41112,7 +41112,7 @@
           <t>F | 418呎 (1房)
 $659万
 $15,773/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -41120,7 +41120,7 @@
           <t>G | 538呎 (2房)
 $983万
 $18,270/呎
-(26年-07月)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -41128,7 +41128,7 @@
           <t>H | 573呎 (2房)
 $997万
 $17,396/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -41159,7 +41159,7 @@
           <t>C | 522呎 (2房)
 $831万
 $15,920/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -41167,7 +41167,7 @@
           <t>D | 518呎 (2房)
 $840万
 $16,207/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -41175,7 +41175,7 @@
           <t>E | 437呎 (1房)
 $688万
 $15,732/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -41183,7 +41183,7 @@
           <t>F | 418呎 (1房)
 $656万
 $15,701/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -41191,7 +41191,7 @@
           <t>G | 538呎 (2房)
 $978万
 $18,180/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -41199,7 +41199,7 @@
           <t>H | 573呎 (2房)
 $992万
 $17,311/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -41230,7 +41230,7 @@
           <t>C | 522呎 (2房)
 $827万
 $15,841/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -41238,7 +41238,7 @@
           <t>D | 518呎 (2房)
 $835万
 $16,125/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -41246,7 +41246,7 @@
           <t>E | 437呎 (1房)
 $684万
 $15,654/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -41254,7 +41254,7 @@
           <t>F | 418呎 (1房)
 $653万
 $15,624/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -41262,7 +41262,7 @@
           <t>G | 538呎 (2房)
 $973万
 $18,089/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -41270,7 +41270,7 @@
           <t>H | 573呎 (2房)
 $987万
 $17,223/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -41301,7 +41301,7 @@
           <t>C | 522呎 (2房)
 $815万
 $15,615/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -41309,7 +41309,7 @@
           <t>D | 518呎 (2房)
 $833万
 $16,087/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -41317,7 +41317,7 @@
           <t>E | 437呎 (1房)
 $682万
 $15,616/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -41325,7 +41325,7 @@
           <t>F | 418呎 (1房)
 $674万
 $16,132/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -41333,7 +41333,7 @@
           <t>G | 538呎 (2房)
 $971万
 $18,045/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -41341,7 +41341,7 @@
           <t>H | 573呎 (2房)
 $973万
 $16,979/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -41372,7 +41372,7 @@
           <t>C | 522呎 (2房)
 $819万
 $15,684/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -41380,7 +41380,7 @@
           <t>D | 518呎 (2房)
 $827万
 $15,967/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -41388,7 +41388,7 @@
           <t>E | 437呎 (1房)
 $677万
 $15,499/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -41396,7 +41396,7 @@
           <t>F | 418呎 (1房)
 $639万
 $15,285/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -41404,7 +41404,7 @@
           <t>G | 538呎 (2房)
 $964万
 $17,911/呎
-(26年-07月)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -41412,7 +41412,7 @@
           <t>H | 573呎 (2房)
 $966万
 $16,853/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -41443,7 +41443,7 @@
           <t>C | 522呎 (2房)
 $805万
 $15,423/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -41451,7 +41451,7 @@
           <t>D | 518呎 (2房)
 $823万
 $15,888/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -41459,7 +41459,7 @@
           <t>E | 437呎 (1房)
 $674万
 $15,421/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -41467,7 +41467,7 @@
           <t>F | 418呎 (1房)
 $643万
 $15,392/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -41475,7 +41475,7 @@
           <t>G | 538呎 (2房)
 $959万
 $17,820/呎
-(26年-07月)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -41483,7 +41483,7 @@
           <t>H | 573呎 (2房)
 $972万
 $16,967/呎
-(26年-04月)</t>
+(26年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -41514,7 +41514,7 @@
           <t>C | 522呎 (2房)
 $811万
 $15,529/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -41522,7 +41522,7 @@
           <t>D | 518呎 (2房)
 $819万
 $15,807/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -41530,7 +41530,7 @@
           <t>E | 437呎 (1房)
 $671万
 $15,346/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -41538,7 +41538,7 @@
           <t>F | 418呎 (1房)
 $633万
 $15,148/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -41546,7 +41546,7 @@
           <t>G | 538呎 (2房)
 $954万
 $17,732/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -41554,7 +41554,7 @@
           <t>H | 573呎 (2房)
 $968万
 $16,885/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -41803,7 +41803,7 @@
           <t>C | 547呎 (2房)
 $1039万
 $18,987/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -41835,7 +41835,7 @@
           <t>G | 554呎 (2房)
 $1175万
 $21,215/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -41874,7 +41874,7 @@
           <t>C | 547呎 (2房)
 $1023万
 $18,707/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -41882,7 +41882,7 @@
           <t>D | 538呎 (2房)
 $994万
 $18,485/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -41906,7 +41906,7 @@
           <t>G | 554呎 (2房)
 $1158万
 $20,903/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -41945,7 +41945,7 @@
           <t>C | 547呎 (2房)
 $1008万
 $18,431/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -41977,7 +41977,7 @@
           <t>G | 554呎 (2房)
 $1141万
 $20,592/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -42016,7 +42016,7 @@
           <t>C | 547呎 (2房)
 $996万
 $18,212/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -42048,7 +42048,7 @@
           <t>G | 554呎 (2房)
 $1127万
 $20,348/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -42087,7 +42087,7 @@
           <t>C | 547呎 (2房)
 $984万
 $17,996/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -42119,7 +42119,7 @@
           <t>G | 554呎 (2房)
 $1114万
 $20,106/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -42158,7 +42158,7 @@
           <t>C | 547呎 (2房)
 $977万
 $17,854/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -42166,7 +42166,7 @@
           <t>D | 538呎 (2房)
 $976万
 $18,139/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -42190,7 +42190,7 @@
           <t>G | 554呎 (2房)
 $1103万
 $19,908/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -42229,7 +42229,7 @@
           <t>C | 547呎 (2房)
 $973万
 $17,782/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -42237,7 +42237,7 @@
           <t>D | 538呎 (2房)
 $955万
 $17,747/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -42253,7 +42253,7 @@
           <t>F | 512呎 (2房)
 $893万
 $17,436/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -42261,7 +42261,7 @@
           <t>G | 554呎 (2房)
 $1097万
 $19,809/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -42300,7 +42300,7 @@
           <t>C | 547呎 (2房)
 $967万
 $17,676/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -42308,7 +42308,7 @@
           <t>D | 538呎 (2房)
 $949万
 $17,641/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -42324,7 +42324,7 @@
           <t>F | 512呎 (2房)
 $887万
 $17,330/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -42332,7 +42332,7 @@
           <t>G | 554呎 (2房)
 $1084万
 $19,574/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -42371,7 +42371,7 @@
           <t>C | 547呎 (2房)
 $963万
 $17,607/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -42379,7 +42379,7 @@
           <t>D | 538呎 (2房)
 $945万
 $17,572/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -42395,7 +42395,7 @@
           <t>F | 512呎 (2房)
 $884万
 $17,262/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -42403,7 +42403,7 @@
           <t>G | 554呎 (2房)
 $1076万
 $19,419/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -42411,7 +42411,7 @@
           <t>H | 573呎 (2房)
 $1197万
 $20,883/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -42442,7 +42442,7 @@
           <t>C | 547呎 (2房)
 $959万
 $17,536/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -42450,7 +42450,7 @@
           <t>D | 538呎 (2房)
 $942万
 $17,500/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -42466,7 +42466,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,193/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -42474,7 +42474,7 @@
           <t>G | 554呎 (2房)
 $1067万
 $19,265/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -42513,7 +42513,7 @@
           <t>C | 547呎 (2房)
 $955万
 $17,466/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -42521,7 +42521,7 @@
           <t>D | 538呎 (2房)
 $938万
 $17,431/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -42537,7 +42537,7 @@
           <t>F | 512呎 (2房)
 $877万
 $17,125/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -42545,7 +42545,7 @@
           <t>G | 554呎 (2房)
 $1059万
 $19,112/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -42584,7 +42584,7 @@
           <t>C | 547呎 (2房)
 $952万
 $17,397/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -42592,7 +42592,7 @@
           <t>D | 538呎 (2房)
 $934万
 $17,362/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -42616,7 +42616,7 @@
           <t>G | 554呎 (2房)
 $1050万
 $18,958/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -42655,7 +42655,7 @@
           <t>C | 547呎 (2房)
 $937万
 $17,122/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -42663,7 +42663,7 @@
           <t>D | 538呎 (2房)
 $930万
 $17,294/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -42687,7 +42687,7 @@
           <t>G | 554呎 (2房)
 $1042万
 $18,809/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -42695,7 +42695,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,229/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42726,7 @@
           <t>C | 547呎 (2房)
 $944万
 $17,258/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -42734,7 +42734,7 @@
           <t>D | 538呎 (2房)
 $927万
 $17,225/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -42758,7 +42758,7 @@
           <t>G | 554呎 (2房)
 $1034万
 $18,661/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -42797,7 +42797,7 @@
           <t>C | 547呎 (2房)
 $940万
 $17,190/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -42805,7 +42805,7 @@
           <t>D | 538呎 (2房)
 $923万
 $17,154/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -42821,7 +42821,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,191/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -42829,7 +42829,7 @@
           <t>G | 554呎 (2房)
 $1026万
 $18,511/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -42868,7 +42868,7 @@
           <t>C | 547呎 (2房)
 $938万
 $17,155/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -42876,7 +42876,7 @@
           <t>D | 538呎 (2房)
 $921万
 $17,121/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -42892,7 +42892,7 @@
           <t>F | 512呎 (2房)
 $878万
 $17,156/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -42900,7 +42900,7 @@
           <t>G | 554呎 (2房)
 $1022万
 $18,451/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -42939,7 +42939,7 @@
           <t>C | 547呎 (2房)
 $933万
 $17,053/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -42947,7 +42947,7 @@
           <t>D | 538呎 (2房)
 $905万
 $16,818/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -42963,7 +42963,7 @@
           <t>F | 512呎 (2房)
 $856万
 $16,719/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -42971,7 +42971,7 @@
           <t>G | 554呎 (2房)
 $1012万
 $18,274/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -42979,7 +42979,7 @@
           <t>H | 573呎 (2房)
 $1126万
 $19,653/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -43010,7 +43010,7 @@
           <t>C | 547呎 (2房)
 $902万
 $16,484/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -43018,7 +43018,7 @@
           <t>D | 538呎 (2房)
 $912万
 $16,952/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43034,7 +43034,7 @@
           <t>F | 512呎 (2房)
 $853万
 $16,652/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -43042,7 +43042,7 @@
           <t>G | 554呎 (2房)
 $996万
 $17,969/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -43081,7 +43081,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,718/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -43089,7 +43089,7 @@
           <t>D | 538呎 (2房)
 $908万
 $16,885/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43105,7 +43105,7 @@
           <t>F | 512呎 (2房)
 $849万
 $16,586/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -43113,7 +43113,7 @@
           <t>G | 554呎 (2房)
 $1002万
 $18,092/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -43152,7 +43152,7 @@
           <t>C | 547呎 (2房)
 $922万
 $16,850/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -43160,7 +43160,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,619/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -43168,7 +43168,7 @@
           <t>E | 537呎 (2房)
 $907万
 $16,885/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -43176,7 +43176,7 @@
           <t>F | 512呎 (2房)
 $846万
 $16,520/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -43184,7 +43184,7 @@
           <t>G | 554呎 (2房)
 $986万
 $17,791/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -43223,7 +43223,7 @@
           <t>C | 547呎 (2房)
 $918万
 $16,782/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -43231,7 +43231,7 @@
           <t>D | 538呎 (2房)
 $901万
 $16,751/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -43247,7 +43247,7 @@
           <t>F | 512呎 (2房)
 $842万
 $16,453/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -43255,7 +43255,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,913/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -43294,7 +43294,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,715/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -43302,7 +43302,7 @@
           <t>D | 538呎 (2房)
 $887万
 $16,487/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -43318,7 +43318,7 @@
           <t>F | 512呎 (2房)
 $839万
 $16,389/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -43326,7 +43326,7 @@
           <t>G | 554呎 (2房)
 $987万
 $17,823/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -43365,7 +43365,7 @@
           <t>C | 547呎 (2房)
 $911万
 $16,649/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -43373,7 +43373,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,615/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -43381,7 +43381,7 @@
           <t>E | 537呎 (2房)
 $878万
 $16,356/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -43389,7 +43389,7 @@
           <t>F | 512呎 (2房)
 $836万
 $16,324/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -43397,7 +43397,7 @@
           <t>G | 554呎 (2房)
 $982万
 $17,735/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -43436,7 +43436,7 @@
           <t>C | 547呎 (2房)
 $907万
 $16,581/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -43444,7 +43444,7 @@
           <t>D | 538呎 (2房)
 $922万
 $17,134/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -43452,7 +43452,7 @@
           <t>E | 537呎 (2房)
 $875万
 $16,291/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -43460,7 +43460,7 @@
           <t>F | 512呎 (2房)
 $832万
 $16,258/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -43468,7 +43468,7 @@
           <t>G | 554呎 (2房)
 $978万
 $17,648/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -43507,7 +43507,7 @@
           <t>C | 547呎 (2房)
 $905万
 $16,550/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -43515,7 +43515,7 @@
           <t>D | 538呎 (2房)
 $889万
 $16,517/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -43523,7 +43523,7 @@
           <t>E | 537呎 (2房)
 $873万
 $16,259/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -43531,7 +43531,7 @@
           <t>F | 512呎 (2房)
 $831万
 $16,227/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -43539,7 +43539,7 @@
           <t>G | 554呎 (2房)
 $964万
 $17,395/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -43578,7 +43578,7 @@
           <t>C | 547呎 (2房)
 $900万
 $16,452/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -43586,7 +43586,7 @@
           <t>D | 538呎 (2房)
 $883万
 $16,418/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -43594,7 +43594,7 @@
           <t>E | 537呎 (2房)
 $868万
 $16,162/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -43602,7 +43602,7 @@
           <t>F | 512呎 (2房)
 $826万
 $16,131/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -43610,7 +43610,7 @@
           <t>G | 554呎 (2房)
 $968万
 $17,471/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -43649,7 +43649,7 @@
           <t>C | 547呎 (2房)
 $896万
 $16,384/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -43657,7 +43657,7 @@
           <t>D | 538呎 (2房)
 $870万
 $16,162/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -43665,7 +43665,7 @@
           <t>E | 537呎 (2房)
 $864万
 $16,099/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -43673,7 +43673,7 @@
           <t>F | 512呎 (2房)
 $822万
 $16,064/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -43681,7 +43681,7 @@
           <t>G | 554呎 (2房)
 $963万
 $17,384/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -43720,7 +43720,7 @@
           <t>C | 547呎 (2房)
 $893万
 $16,320/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -43728,7 +43728,7 @@
           <t>D | 538呎 (2房)
 $876万
 $16,288/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -43736,7 +43736,7 @@
           <t>E | 537呎 (2房)
 $861万
 $16,034/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -43744,7 +43744,7 @@
           <t>F | 512呎 (2房)
 $819万
 $16,000/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -43752,7 +43752,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,908/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -43760,7 +43760,7 @@
           <t>H | 573呎 (2房)
 $1066万
 $18,604/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -43791,7 +43791,7 @@
           <t>C | 547呎 (2房)
 $889万
 $16,256/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -43799,7 +43799,7 @@
           <t>D | 538呎 (2房)
 $873万
 $16,223/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -43807,7 +43807,7 @@
           <t>E | 537呎 (2房)
 $858万
 $15,970/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -43815,7 +43815,7 @@
           <t>F | 512呎 (2房)
 $816万
 $15,938/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -43823,7 +43823,7 @@
           <t>G | 554呎 (2房)
 $954万
 $17,211/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -43862,7 +43862,7 @@
           <t>C | 547呎 (2房)
 $886万
 $16,190/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -43870,7 +43870,7 @@
           <t>D | 538呎 (2房)
 $869万
 $16,158/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -43878,7 +43878,7 @@
           <t>E | 537呎 (2房)
 $854万
 $15,907/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -43886,7 +43886,7 @@
           <t>F | 512呎 (2房)
 $813万
 $15,875/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -43894,7 +43894,7 @@
           <t>G | 554呎 (2房)
 $949万
 $17,128/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -43902,7 +43902,7 @@
           <t>H | 573呎 (2房)
 $1045万
 $18,237/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -43933,7 +43933,7 @@
           <t>C | 547呎 (2房)
 $882万
 $16,117/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -43941,7 +43941,7 @@
           <t>D | 538呎 (2房)
 $866万
 $16,087/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -43949,7 +43949,7 @@
           <t>E | 537呎 (2房)
 $850万
 $15,834/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -43957,7 +43957,7 @@
           <t>F | 512呎 (2房)
 $809万
 $15,803/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -43965,7 +43965,7 @@
           <t>G | 554呎 (2房)
 $944万
 $17,042/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -43973,7 +43973,7 @@
           <t>H | 573呎 (2房)
 $1040万
 $18,147/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -44004,7 +44004,7 @@
           <t>C | 547呎 (2房)
 $878万
 $16,046/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -44012,7 +44012,7 @@
           <t>D | 538呎 (2房)
 $862万
 $16,015/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -44020,7 +44020,7 @@
           <t>E | 537呎 (2房)
 $846万
 $15,764/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -44028,7 +44028,7 @@
           <t>F | 512呎 (2房)
 $834万
 $16,287/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -44036,7 +44036,7 @@
           <t>G | 554呎 (2房)
 $939万
 $16,957/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -44044,7 +44044,7 @@
           <t>H | 573呎 (2房)
 $1035万
 $18,056/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44075,7 +44075,7 @@
           <t>C | 547呎 (2房)
 $873万
 $15,965/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -44083,7 +44083,7 @@
           <t>D | 538呎 (2房)
 $888万
 $16,498/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -44091,7 +44091,7 @@
           <t>E | 537呎 (2房)
 $859万
 $15,998/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -44099,7 +44099,7 @@
           <t>F | 512呎 (2房)
 $802万
 $15,654/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -44107,7 +44107,7 @@
           <t>G | 554呎 (2房)
 $924万
 $16,673/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -44115,7 +44115,7 @@
           <t>H | 573呎 (2房)
 $1029万
 $17,965/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44146,7 @@
           <t>C | 547呎 (2房)
 $872万
 $15,934/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -44154,7 +44154,7 @@
           <t>D | 538呎 (2房)
 $886万
 $16,463/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -44162,7 +44162,7 @@
           <t>E | 537呎 (2房)
 $857万
 $15,966/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -44170,7 +44170,7 @@
           <t>F | 512呎 (2房)
 $790万
 $15,438/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -44178,7 +44178,7 @@
           <t>G | 554呎 (2房)
 $932万
 $16,830/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -44186,7 +44186,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,921/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
           <t>C | 547呎 (2房)
 $866万
 $15,839/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -44225,7 +44225,7 @@
           <t>D | 538呎 (2房)
 $850万
 $15,807/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -44233,7 +44233,7 @@
           <t>E | 537呎 (2房)
 $852万
 $15,872/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -44241,7 +44241,7 @@
           <t>F | 512呎 (2房)
 $795万
 $15,529/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -44249,7 +44249,7 @@
           <t>G | 554呎 (2房)
 $926万
 $16,706/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -44257,7 +44257,7 @@
           <t>H | 573呎 (2房)
 $1019万
 $17,787/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
           <t>C | 547呎 (2房)
 $862万
 $15,761/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -44296,7 +44296,7 @@
           <t>D | 538呎 (2房)
 $846万
 $15,730/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -44304,7 +44304,7 @@
           <t>E | 537呎 (2房)
 $848万
 $15,791/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -44312,7 +44312,7 @@
           <t>F | 512呎 (2房)
 $791万
 $15,453/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -44320,7 +44320,7 @@
           <t>G | 554呎 (2房)
 $921万
 $16,623/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I40" s="21" t="inlineStr">
@@ -44328,7 +44328,7 @@
           <t>H | 573呎 (2房)
 $1014万
 $17,698/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -44359,7 +44359,7 @@
           <t>C | 547呎 (2房)
 $858万
 $15,682/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -44367,7 +44367,7 @@
           <t>D | 538呎 (2房)
 $842万
 $15,651/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -44375,7 +44375,7 @@
           <t>E | 537呎 (2房)
 $844万
 $15,715/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
@@ -44383,7 +44383,7 @@
           <t>F | 512呎 (2房)
 $788万
 $15,398/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
@@ -44391,7 +44391,7 @@
           <t>G | 554呎 (2房)
 $916万
 $16,540/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -44399,7 +44399,7 @@
           <t>H | 573呎 (2房)
 $1009万
 $17,611/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
     </row>
